--- a/artfynd/A 538-2023 artfynd.xlsx
+++ b/artfynd/A 538-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 538-2023 artfynd.xlsx
+++ b/artfynd/A 538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110909613</v>
+        <v>110909943</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451565.106855567</v>
+        <v>451508</v>
       </c>
       <c r="R2" t="n">
-        <v>7181760.458514133</v>
+        <v>7181923</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,19 +744,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110910567</v>
+        <v>110909969</v>
       </c>
       <c r="B3" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451620</v>
+        <v>451518</v>
       </c>
       <c r="R3" t="n">
-        <v>7182052</v>
+        <v>7181954</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,11 +845,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110910548</v>
+        <v>110910617</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451608.2631430762</v>
+        <v>451635</v>
       </c>
       <c r="R4" t="n">
-        <v>7182051.821949059</v>
+        <v>7182062</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110910617</v>
+        <v>110910548</v>
       </c>
       <c r="B5" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451635.3453914287</v>
+        <v>451609</v>
       </c>
       <c r="R5" t="n">
-        <v>7182061.207297631</v>
+        <v>7182052</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110910100</v>
+        <v>110909709</v>
       </c>
       <c r="B6" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451470.7043345092</v>
+        <v>451551</v>
       </c>
       <c r="R6" t="n">
-        <v>7182030.977978008</v>
+        <v>7181864</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110910540</v>
+        <v>110910009</v>
       </c>
       <c r="B7" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,21 +1195,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451608</v>
+        <v>451478</v>
       </c>
       <c r="R7" t="n">
-        <v>7182052</v>
+        <v>7181973</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,24 +1234,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,15 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110909943</v>
+        <v>110910149</v>
       </c>
       <c r="B8" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,35 +1279,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451507.86490747</v>
+        <v>451433</v>
       </c>
       <c r="R8" t="n">
-        <v>7181922.782331771</v>
+        <v>7182025</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1439,7 +1344,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1354,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,15 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110910405</v>
+        <v>110910367</v>
       </c>
       <c r="B9" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451597</v>
+        <v>451572</v>
       </c>
       <c r="R9" t="n">
-        <v>7182059</v>
+        <v>7182065</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1599,15 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110910009</v>
+        <v>110910405</v>
       </c>
       <c r="B10" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,16 +1534,21 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451478</v>
+        <v>451597</v>
       </c>
       <c r="R10" t="n">
-        <v>7181973</v>
+        <v>7182059</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,9 +1578,19 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1707,51 +1622,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110909709</v>
+        <v>110910540</v>
       </c>
       <c r="B11" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451551.814869214</v>
+        <v>451609</v>
       </c>
       <c r="R11" t="n">
-        <v>7181864.432409053</v>
+        <v>7182052</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1708,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,15 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110910149</v>
+        <v>110910567</v>
       </c>
       <c r="B12" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,21 +1770,16 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451433</v>
+        <v>451620</v>
       </c>
       <c r="R12" t="n">
-        <v>7182025</v>
+        <v>7182052</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,24 +1809,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,15 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110910367</v>
+        <v>110909613</v>
       </c>
       <c r="B13" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,28 +1854,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451572</v>
+        <v>451565</v>
       </c>
       <c r="R13" t="n">
-        <v>7182064</v>
+        <v>7181760</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2022,24 +1917,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,119 +1943,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>110909969</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Vallån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>451518.6236811291</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7181953.778723399</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 538-2023 artfynd.xlsx
+++ b/artfynd/A 538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110909943</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110909969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910548</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110909709</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910009</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910149</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910540</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1840,6 +1895,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110910567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,8 +2003,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110909613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>